--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/6613-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/6613-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{66FE421D-1D02-44C9-9C8C-479929E59CDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{44B931C0-5087-4330-9789-A78DBDA7B611}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{A80C8D66-B0B3-4E7D-89E2-E9986DA3EBA1}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{257AB639-6CDC-4720-93A6-BAB98F0751CE}"/>
   </bookViews>
   <sheets>
     <sheet name="6613-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1519,30 +1519,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7985B05-A0EC-4BEA-921B-ED4D05B38B67}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAB13264-3D38-4959-B044-790C9FD8C13D}">
   <dimension ref="A1:X24"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="6" width="7.125" customWidth="1"/>
-    <col min="7" max="9" width="6.75" customWidth="1"/>
-    <col min="10" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="14" width="7.125" customWidth="1"/>
-    <col min="15" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="8.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.625" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="6" width="6.109375" customWidth="1"/>
+    <col min="7" max="9" width="5.88671875" customWidth="1"/>
+    <col min="10" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="14" width="6.109375" customWidth="1"/>
+    <col min="15" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="7" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1576,7 +1576,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1612,7 +1612,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1732,7 +1732,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1804,7 +1804,7 @@
         <v>3.31</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="39"/>
       <c r="B6" s="40"/>
       <c r="C6" s="42"/>
@@ -1840,7 +1840,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>30</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>1.66</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="47">
         <v>2024</v>
       </c>
@@ -1986,7 +1986,7 @@
         <v>8.56</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
         <v>30</v>
       </c>
@@ -2060,7 +2060,7 @@
         <v>6.47</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="18" t="s">
         <v>30</v>
       </c>
@@ -2134,7 +2134,7 @@
         <v>2.09</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="49">
         <v>2023</v>
       </c>
@@ -2206,7 +2206,7 @@
         <v>7.78</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>30</v>
       </c>
@@ -2280,7 +2280,7 @@
         <v>5.21</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>30</v>
       </c>
@@ -2354,7 +2354,7 @@
         <v>2.57</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="47">
         <v>2022</v>
       </c>
@@ -2426,7 +2426,7 @@
         <v>9.89</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
         <v>30</v>
       </c>
@@ -2500,7 +2500,7 @@
         <v>7.56</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="18" t="s">
         <v>30</v>
       </c>
@@ -2574,7 +2574,7 @@
         <v>2.33</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="49">
         <v>2021</v>
       </c>
@@ -2646,7 +2646,7 @@
         <v>15.1</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="47">
         <v>2020</v>
       </c>
@@ -2718,7 +2718,7 @@
         <v>6.3</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="49">
         <v>2019</v>
       </c>
@@ -2790,7 +2790,7 @@
         <v>8.0299999999999994</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="47">
         <v>2018</v>
       </c>
@@ -2862,7 +2862,7 @@
         <v>11.4</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="49">
         <v>2017</v>
       </c>
@@ -2934,7 +2934,7 @@
         <v>7.25</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="47">
         <v>2016</v>
       </c>
@@ -3006,7 +3006,7 @@
         <v>7.38</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="49">
         <v>2015</v>
       </c>
@@ -3078,7 +3078,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="47" t="s">
         <v>46</v>
       </c>
